--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlMode.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlMode.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t xml:space="preserve">放置4个木桩，每个木桩死亡后定时复活刷新。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">练习赛（测试）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对抗bot</t>
   </si>
 </sst>
 </file>
@@ -808,6 +814,29 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlMode.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlMode.xlsx
@@ -155,7 +155,7 @@
     <t xml:space="preserve">放置4个木桩，每个木桩死亡后定时复活刷新。</t>
   </si>
   <si>
-    <t xml:space="preserve">练习赛（测试）</t>
+    <t xml:space="preserve">练习赛</t>
   </si>
   <si>
     <t xml:space="preserve">对抗bot</t>
